--- a/Employee_Reports_wi52/Ifran Ansari Q0600.xlsx
+++ b/Employee_Reports_wi52/Ifran Ansari Q0600.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-59</v>
+        <v>-67</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1328,78 +1328,78 @@
       <c r="K18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1522,11 +1522,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1599,20 +1599,20 @@
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>22-Aug-2028</t>
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>315</v>
+        <v>725</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1756,123 +1756,123 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>Consignment Shuttle Tv</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>77.36%</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Approved Score. date is valid</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>Turntable &amp; Ra Deck</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>05-Aug-2026</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>92.11%</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Cs Hoist</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>31-Jul-2025</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>55.56%</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Uld Hoist</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>15-Sep-2025</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>80.00%</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Truck Dock</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>26-May-2026</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>69.62%</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>low percentage</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1880,78 +1880,109 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>Truck Dock</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>26-May-2026</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>69.62%</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>low percentage</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>Cool Rooms</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>24-Aug-2025</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>59.73%</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Climate Control Center</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>04-Sep-2025</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>76.66%</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>TOTAL AVERAGE</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>74.64%</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>74.95%</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2039,7 +2070,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2134,7 +2165,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2163,7 +2194,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2192,7 +2223,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2252,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2250,7 +2281,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2310,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2308,7 +2339,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2337,7 +2368,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2397,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2395,7 +2426,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2424,7 +2455,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2453,7 +2484,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2482,7 +2513,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2511,7 +2542,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2540,7 +2571,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2569,7 +2600,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2598,7 +2629,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2627,7 +2658,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2687,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
